--- a/data/trans_orig/P6708-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6708-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se tiene en cuenta su opinión cuando se le asignan las tareas en 2012</t>
+          <t>Población según si se tiene en cuenta su opinión cuando se le asignan las tareas en 2012 (tasa de respuesta: 99,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>6708</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21994</t>
+          <t>21793</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11773</t>
+          <t>12177</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27493</t>
+          <t>28476</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21755</t>
+          <t>21082</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43750</t>
+          <t>43015</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>17182</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>6769</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21991</t>
+          <t>22166</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13343</t>
+          <t>13810</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32763</t>
+          <t>33152</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26996</t>
+          <t>26673</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49446</t>
+          <t>49923</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>12240</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32233</t>
+          <t>30282</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44697</t>
+          <t>43642</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73035</t>
+          <t>73750</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24418</t>
+          <t>24400</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45515</t>
+          <t>47100</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14599</t>
+          <t>14377</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31944</t>
+          <t>32200</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>43498</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71510</t>
+          <t>72066</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76151</t>
+          <t>76057</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>103415</t>
+          <t>102739</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54689</t>
+          <t>53923</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>78259</t>
+          <t>77596</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>138339</t>
+          <t>136185</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>173359</t>
+          <t>173024</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,56%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65029</t>
+          <t>65375</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>102159</t>
+          <t>101469</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40622</t>
+          <t>39048</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67734</t>
+          <t>66158</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111396</t>
+          <t>111949</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159537</t>
+          <t>157731</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63937</t>
+          <t>61782</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99127</t>
+          <t>100199</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38508</t>
+          <t>38129</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68439</t>
+          <t>68308</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111565</t>
+          <t>110811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>156577</t>
+          <t>156117</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>168814</t>
+          <t>166886</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>217123</t>
+          <t>215821</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>107235</t>
+          <t>108661</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>150086</t>
+          <t>148454</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>286210</t>
+          <t>287108</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>350911</t>
+          <t>351489</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>197923</t>
+          <t>197417</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>251930</t>
+          <t>250847</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120716</t>
+          <t>120914</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>161326</t>
+          <t>162301</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>332396</t>
+          <t>327325</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>398696</t>
+          <t>398740</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>307524</t>
+          <t>307727</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>366824</t>
+          <t>368572</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>176853</t>
+          <t>175913</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>221752</t>
+          <t>223440</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>497756</t>
+          <t>496332</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>575226</t>
+          <t>574849</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,81%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22750</t>
+          <t>25335</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>10738</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29285</t>
+          <t>29396</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20857</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45223</t>
+          <t>44894</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27019</t>
+          <t>28089</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21831</t>
+          <t>20955</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18159</t>
+          <t>18300</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40738</t>
+          <t>41595</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45254</t>
+          <t>45539</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74515</t>
+          <t>74051</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42736</t>
+          <t>41823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>70855</t>
+          <t>71157</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>95139</t>
+          <t>93292</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>135697</t>
+          <t>134404</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74770</t>
+          <t>73542</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>108885</t>
+          <t>109100</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47955</t>
+          <t>48490</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77217</t>
+          <t>78733</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>131108</t>
+          <t>130763</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>177519</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>120920</t>
+          <t>119477</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>157261</t>
+          <t>157576</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71963</t>
+          <t>72557</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>103817</t>
+          <t>102918</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>199084</t>
+          <t>200990</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>249798</t>
+          <t>249667</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,3%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85822</t>
+          <t>86242</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>128397</t>
+          <t>130871</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>71691</t>
+          <t>73056</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>109286</t>
+          <t>110020</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>171048</t>
+          <t>169052</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>227654</t>
+          <t>224983</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>87866</t>
+          <t>86911</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>131307</t>
+          <t>129542</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>61603</t>
+          <t>62540</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>95865</t>
+          <t>96490</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>157698</t>
+          <t>158429</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>212048</t>
+          <t>214276</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>256156</t>
+          <t>256018</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>319947</t>
+          <t>319031</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>174872</t>
+          <t>178518</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>228856</t>
+          <t>230055</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>449834</t>
+          <t>449977</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>533125</t>
+          <t>529667</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>312964</t>
+          <t>314253</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>383091</t>
+          <t>383739</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>197189</t>
+          <t>196841</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>251666</t>
+          <t>249715</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>525865</t>
+          <t>531506</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>609833</t>
+          <t>613522</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>527953</t>
+          <t>523161</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>603046</t>
+          <t>600985</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>321967</t>
+          <t>323221</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>383081</t>
+          <t>385823</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>865982</t>
+          <t>867844</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>966028</t>
+          <t>962525</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,86%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se tiene en cuenta su opinión cuando se le asignan las tareas en 2016</t>
+          <t>Población según si se tiene en cuenta su opinión cuando se le asignan las tareas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>16099</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36232</t>
+          <t>35820</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18278</t>
+          <t>17860</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25156</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50436</t>
+          <t>47553</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17548</t>
+          <t>17931</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35939</t>
+          <t>36466</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9231</t>
+          <t>8634</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22662</t>
+          <t>22616</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30057</t>
+          <t>30470</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53294</t>
+          <t>54667</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22738</t>
+          <t>23107</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43374</t>
+          <t>43683</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24184</t>
+          <t>23775</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35629</t>
+          <t>37378</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>60251</t>
+          <t>61361</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13670</t>
+          <t>14020</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31683</t>
+          <t>31533</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19962</t>
+          <t>19633</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24134</t>
+          <t>24226</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44747</t>
+          <t>46083</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28718</t>
+          <t>28076</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49548</t>
+          <t>49654</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>11064</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24805</t>
+          <t>25825</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42954</t>
+          <t>42949</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>68559</t>
+          <t>69129</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75510</t>
+          <t>77722</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115798</t>
+          <t>114401</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57374</t>
+          <t>58367</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92292</t>
+          <t>90571</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>143808</t>
+          <t>145514</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191967</t>
+          <t>196240</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105379</t>
+          <t>106347</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>145795</t>
+          <t>150474</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81301</t>
+          <t>79948</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>119097</t>
+          <t>115554</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>195968</t>
+          <t>196841</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>252239</t>
+          <t>251724</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>239335</t>
+          <t>243018</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>297175</t>
+          <t>295814</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>165912</t>
+          <t>164268</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211411</t>
+          <t>209403</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>417769</t>
+          <t>417735</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>491771</t>
+          <t>490421</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,08%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>187685</t>
+          <t>188209</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>242570</t>
+          <t>240755</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>139757</t>
+          <t>141396</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>183551</t>
+          <t>186745</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>341876</t>
+          <t>340867</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>407853</t>
+          <t>408655</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>196961</t>
+          <t>201465</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>253868</t>
+          <t>252918</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>112142</t>
+          <t>112215</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>154451</t>
+          <t>154776</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>328619</t>
+          <t>323420</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>392938</t>
+          <t>390144</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26225</t>
+          <t>25838</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25144</t>
+          <t>24950</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49144</t>
+          <t>48010</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38260</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66843</t>
+          <t>67644</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31718</t>
+          <t>30954</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56194</t>
+          <t>56620</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32832</t>
+          <t>34099</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57729</t>
+          <t>58592</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,47 +5218,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>11,05%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>19,0%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>87139</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>70146</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>104458</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>13,22%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>10,64%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>18,72%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>87139</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>70836</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>103599</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>13,22%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>77038</t>
+          <t>78802</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>112895</t>
+          <t>114681</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55015</t>
+          <t>55781</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>85471</t>
+          <t>85024</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>141600</t>
+          <t>144033</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>187459</t>
+          <t>192261</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>29,17%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73942</t>
+          <t>74498</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>106266</t>
+          <t>107852</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52291</t>
+          <t>51916</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81604</t>
+          <t>79672</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>132945</t>
+          <t>133058</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>173902</t>
+          <t>176418</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,77%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>88971</t>
+          <t>90606</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123727</t>
+          <t>127224</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78799</t>
+          <t>78004</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>113530</t>
+          <t>110879</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>178951</t>
+          <t>179607</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>228069</t>
+          <t>230785</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>35,02%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>115879</t>
+          <t>113431</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>163572</t>
+          <t>160887</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>100176</t>
+          <t>100228</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>144275</t>
+          <t>142275</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>228480</t>
+          <t>226611</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>288761</t>
+          <t>288178</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>169738</t>
+          <t>167178</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>222283</t>
+          <t>223841</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>136667</t>
+          <t>138054</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>182596</t>
+          <t>184362</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>319217</t>
+          <t>319512</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>389872</t>
+          <t>387953</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>361297</t>
+          <t>360774</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>431093</t>
+          <t>428563</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>245559</t>
+          <t>243424</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>300717</t>
+          <t>301392</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>623600</t>
+          <t>620835</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>714932</t>
+          <t>711312</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,01%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>289596</t>
+          <t>292878</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>355299</t>
+          <t>356156</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>213557</t>
+          <t>214773</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>267511</t>
+          <t>269148</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>520602</t>
+          <t>518682</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>604493</t>
+          <t>602815</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>338716</t>
+          <t>340703</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>406298</t>
+          <t>410606</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>215482</t>
+          <t>212528</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>270254</t>
+          <t>270895</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>571340</t>
+          <t>570596</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>659850</t>
+          <t>659421</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se tiene en cuenta su opinión cuando se le asignan las tareas en 2023</t>
+          <t>Población según si se tiene en cuenta su opinión cuando se le asignan las tareas en 2023 (tasa de respuesta: 99,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>10347</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1620</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14571</t>
+          <t>14236</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11960</t>
+          <t>12956</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>716</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>15070</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8088</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20730</t>
+          <t>21005</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10508</t>
+          <t>10835</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14827</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28505</t>
+          <t>28995</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>57,42%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2933</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11536</t>
+          <t>11775</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>524</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13701</t>
+          <t>14212</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>28,15%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>811</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11337</t>
+          <t>10378</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11140</t>
+          <t>10625</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81943</t>
+          <t>82680</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40009</t>
+          <t>40918</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61775</t>
+          <t>62809</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37061</t>
+          <t>35981</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140317</t>
+          <t>140697</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11914</t>
+          <t>10796</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89786</t>
+          <t>90263</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26881</t>
+          <t>26313</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46935</t>
+          <t>48019</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32995</t>
+          <t>28912</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128879</t>
+          <t>127970</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23100</t>
+          <t>21369</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>161882</t>
+          <t>159470</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50904</t>
+          <t>51407</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74236</t>
+          <t>73970</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>55079</t>
+          <t>57692</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>220227</t>
+          <t>221498</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>12623</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95823</t>
+          <t>94580</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27978</t>
+          <t>27863</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46981</t>
+          <t>47686</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31188</t>
+          <t>33759</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131408</t>
+          <t>130037</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109250</t>
+          <t>111435</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>443643</t>
+          <t>454710</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32881</t>
+          <t>30979</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54076</t>
+          <t>53834</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>145026</t>
+          <t>146930</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>576198</t>
+          <t>582946</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>78,77%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>12448</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30234</t>
+          <t>30855</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12547</t>
+          <t>11947</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25507</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27513</t>
+          <t>28677</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50156</t>
+          <t>51080</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17577</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3539</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>13628</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11220</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27442</t>
+          <t>27129</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21190</t>
+          <t>21974</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42915</t>
+          <t>43264</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>17690</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32027</t>
+          <t>32745</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>43552</t>
+          <t>43683</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>70746</t>
+          <t>69462</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16421</t>
+          <t>15713</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35139</t>
+          <t>34188</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20415</t>
+          <t>21201</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37599</t>
+          <t>38516</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>42050</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65573</t>
+          <t>66477</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27626</t>
+          <t>27440</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50855</t>
+          <t>51243</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19684</t>
+          <t>19725</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36626</t>
+          <t>35853</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51848</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>79663</t>
+          <t>81163</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22907</t>
+          <t>23300</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105392</t>
+          <t>108235</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59531</t>
+          <t>60567</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>86037</t>
+          <t>88193</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64696</t>
+          <t>68980</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>184668</t>
+          <t>187023</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20679</t>
+          <t>20959</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>98528</t>
+          <t>97375</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35035</t>
+          <t>36178</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>58128</t>
+          <t>59361</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>50304</t>
+          <t>50455</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>146482</t>
+          <t>142421</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>48231</t>
+          <t>42669</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>204842</t>
+          <t>210385</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>79206</t>
+          <t>80545</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>107405</t>
+          <t>109631</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>109173</t>
+          <t>105231</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>295708</t>
+          <t>299847</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,41%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30228</t>
+          <t>28124</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>128887</t>
+          <t>131535</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56535</t>
+          <t>55006</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>82799</t>
+          <t>80689</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>71831</t>
+          <t>72786</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>198995</t>
+          <t>197186</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>154829</t>
+          <t>152053</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>536061</t>
+          <t>552389</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58913</t>
+          <t>58402</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>86940</t>
+          <t>86973</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>222463</t>
+          <t>222639</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>702285</t>
+          <t>714739</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>70,11%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6708-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6708-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21793</t>
+          <t>21480</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12177</t>
+          <t>12108</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28476</t>
+          <t>29754</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21082</t>
+          <t>22466</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43015</t>
+          <t>43851</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17182</t>
+          <t>16470</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22166</t>
+          <t>20691</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13810</t>
+          <t>14676</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33152</t>
+          <t>33419</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26673</t>
+          <t>26818</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49923</t>
+          <t>48812</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12240</t>
+          <t>12491</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30282</t>
+          <t>31240</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43642</t>
+          <t>44059</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73750</t>
+          <t>73914</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24400</t>
+          <t>24823</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47100</t>
+          <t>45199</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14377</t>
+          <t>14544</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32200</t>
+          <t>33080</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43498</t>
+          <t>42956</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72066</t>
+          <t>72658</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76057</t>
+          <t>75948</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102739</t>
+          <t>103157</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53923</t>
+          <t>53335</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>77596</t>
+          <t>78537</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136185</t>
+          <t>136940</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>173024</t>
+          <t>174497</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>54,02%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65375</t>
+          <t>63146</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>101469</t>
+          <t>98925</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39048</t>
+          <t>39914</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66158</t>
+          <t>68167</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111949</t>
+          <t>111459</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157731</t>
+          <t>157967</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61782</t>
+          <t>63889</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100199</t>
+          <t>101808</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38129</t>
+          <t>39008</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68308</t>
+          <t>67808</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110811</t>
+          <t>110896</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>156117</t>
+          <t>155131</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>166886</t>
+          <t>165019</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>215821</t>
+          <t>215406</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>108661</t>
+          <t>106699</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>148454</t>
+          <t>147499</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>287108</t>
+          <t>287254</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>351489</t>
+          <t>352291</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>197417</t>
+          <t>196397</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>250847</t>
+          <t>250428</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120914</t>
+          <t>120873</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162301</t>
+          <t>160332</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>327325</t>
+          <t>327123</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>398740</t>
+          <t>396764</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>307727</t>
+          <t>303919</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368572</t>
+          <t>366639</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>175913</t>
+          <t>175109</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>223440</t>
+          <t>219851</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>496332</t>
+          <t>497100</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>574849</t>
+          <t>572990</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25335</t>
+          <t>23301</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10738</t>
+          <t>10095</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29396</t>
+          <t>29393</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20523</t>
+          <t>20242</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44894</t>
+          <t>44028</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28089</t>
+          <t>28112</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20955</t>
+          <t>21131</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18300</t>
+          <t>18253</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41595</t>
+          <t>42032</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45539</t>
+          <t>45726</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74051</t>
+          <t>75544</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41823</t>
+          <t>41858</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71157</t>
+          <t>68220</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>93292</t>
+          <t>95156</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>134404</t>
+          <t>134255</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73542</t>
+          <t>74276</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109100</t>
+          <t>108359</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48490</t>
+          <t>48144</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78733</t>
+          <t>76776</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>130763</t>
+          <t>131509</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>175518</t>
+          <t>174356</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,63%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119477</t>
+          <t>119782</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>157576</t>
+          <t>155579</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>72557</t>
+          <t>71303</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>102918</t>
+          <t>103484</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>200990</t>
+          <t>199012</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>249667</t>
+          <t>249781</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,32%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>86242</t>
+          <t>87883</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>130871</t>
+          <t>130131</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>73056</t>
+          <t>72581</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>110020</t>
+          <t>109211</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>169052</t>
+          <t>171377</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>224983</t>
+          <t>225355</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>86911</t>
+          <t>84676</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>129542</t>
+          <t>128538</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>62540</t>
+          <t>61250</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>96490</t>
+          <t>95392</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>158429</t>
+          <t>157443</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>214276</t>
+          <t>212018</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>256018</t>
+          <t>258594</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>319031</t>
+          <t>321286</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,82 +3019,82 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>22,77%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>202460</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>179251</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>232122</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>21,43%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>18,98%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>24,57%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>489460</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>449024</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>532671</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>20,78%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>19,06%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
           <t>22,61%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>202460</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>178518</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>230055</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>21,43%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>18,9%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>24,36%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>463</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>489460</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>449977</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>529667</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>20,78%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>19,1%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>314253</t>
+          <t>315975</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>383739</t>
+          <t>383265</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>196841</t>
+          <t>198865</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>249715</t>
+          <t>252273</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>531506</t>
+          <t>530956</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>613522</t>
+          <t>617810</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>523161</t>
+          <t>527226</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>600985</t>
+          <t>602728</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>323221</t>
+          <t>319454</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>385823</t>
+          <t>379687</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>867844</t>
+          <t>866559</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>962525</t>
+          <t>967059</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,06%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16099</t>
+          <t>17071</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35820</t>
+          <t>35411</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17860</t>
+          <t>17391</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25156</t>
+          <t>26773</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47553</t>
+          <t>48017</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17931</t>
+          <t>17425</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36466</t>
+          <t>36454</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8634</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22616</t>
+          <t>23487</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30470</t>
+          <t>30623</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54667</t>
+          <t>52915</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,59%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23107</t>
+          <t>22429</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43683</t>
+          <t>42453</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>9168</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23775</t>
+          <t>22896</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>37378</t>
+          <t>36705</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61361</t>
+          <t>61888</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14020</t>
+          <t>13589</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31533</t>
+          <t>30850</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6967</t>
+          <t>6850</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19633</t>
+          <t>18851</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24226</t>
+          <t>24691</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46083</t>
+          <t>44653</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28076</t>
+          <t>28587</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49654</t>
+          <t>49998</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11064</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25825</t>
+          <t>24596</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42949</t>
+          <t>42970</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69129</t>
+          <t>68710</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77722</t>
+          <t>76510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>114401</t>
+          <t>115511</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58367</t>
+          <t>58853</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90571</t>
+          <t>91150</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,47 +4423,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>9,02%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>13,96%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>168114</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>141068</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>193218</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>8,94%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>13,87%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>168114</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>145514</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>196240</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>10,65%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>9,22%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>106347</t>
+          <t>106774</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>150474</t>
+          <t>147827</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79948</t>
+          <t>80598</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>115554</t>
+          <t>118343</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>196841</t>
+          <t>199013</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>251724</t>
+          <t>256010</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>243018</t>
+          <t>239719</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>295814</t>
+          <t>295209</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164268</t>
+          <t>161919</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>209403</t>
+          <t>208992</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>417735</t>
+          <t>420165</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>490421</t>
+          <t>491059</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>188209</t>
+          <t>185159</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>240755</t>
+          <t>237943</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>141396</t>
+          <t>140403</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>186745</t>
+          <t>186119</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>340867</t>
+          <t>341390</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>408655</t>
+          <t>409470</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>201465</t>
+          <t>201402</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>252918</t>
+          <t>254369</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>112215</t>
+          <t>113092</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>154776</t>
+          <t>152772</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>323420</t>
+          <t>323561</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>390144</t>
+          <t>393242</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25838</t>
+          <t>25444</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24950</t>
+          <t>25056</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48010</t>
+          <t>47856</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38283</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67644</t>
+          <t>67448</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30954</t>
+          <t>29508</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56620</t>
+          <t>56070</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34099</t>
+          <t>32791</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58592</t>
+          <t>57968</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>70146</t>
+          <t>70772</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>104458</t>
+          <t>106817</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>78802</t>
+          <t>78979</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>114681</t>
+          <t>115188</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55781</t>
+          <t>55701</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>85024</t>
+          <t>84439</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>144033</t>
+          <t>141641</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>192261</t>
+          <t>186582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74498</t>
+          <t>72373</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107852</t>
+          <t>106749</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51916</t>
+          <t>51778</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79672</t>
+          <t>78853</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>133058</t>
+          <t>132157</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>176418</t>
+          <t>176312</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90606</t>
+          <t>91564</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>127224</t>
+          <t>128043</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78004</t>
+          <t>78512</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110879</t>
+          <t>110448</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>179607</t>
+          <t>178006</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>230785</t>
+          <t>226078</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,3%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>113431</t>
+          <t>113446</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>160887</t>
+          <t>158789</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>100228</t>
+          <t>101273</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>142275</t>
+          <t>143360</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>226611</t>
+          <t>222928</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>288178</t>
+          <t>286040</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>167178</t>
+          <t>171364</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>223841</t>
+          <t>221648</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>138054</t>
+          <t>137239</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>184362</t>
+          <t>183730</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>319512</t>
+          <t>316965</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>387953</t>
+          <t>390848</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>360774</t>
+          <t>360378</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>428563</t>
+          <t>428918</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>243424</t>
+          <t>245813</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>301392</t>
+          <t>299661</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>620835</t>
+          <t>618313</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>711312</t>
+          <t>710708</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>292878</t>
+          <t>288303</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>356156</t>
+          <t>353217</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>214773</t>
+          <t>214643</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>269148</t>
+          <t>268968</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>518682</t>
+          <t>523669</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>602815</t>
+          <t>605984</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>340703</t>
+          <t>341189</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>410606</t>
+          <t>404537</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>212528</t>
+          <t>217438</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>270895</t>
+          <t>273631</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>570596</t>
+          <t>570238</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>659421</t>
+          <t>664528</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -6645,32 +6645,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>11027</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1456</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>22494</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6680,32 +6680,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>9761</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6715,32 +6715,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>16361</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>9780</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14236</t>
+          <t>28836</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>44,81%</t>
         </is>
       </c>
     </row>
@@ -6758,32 +6758,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12956</t>
+          <t>13932</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6793,32 +6793,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6828,32 +6828,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>9916</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>20077</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -6871,32 +6871,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14678</t>
+          <t>15706</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21005</t>
+          <t>22997</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6906,32 +6906,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7334</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10835</t>
+          <t>12182</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6941,32 +6941,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>22012</t>
+          <t>23530</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15584</t>
+          <t>15565</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28995</t>
+          <t>32737</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>50,87%</t>
         </is>
       </c>
     </row>
@@ -6984,32 +6984,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>2750</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11775</t>
+          <t>12750</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7019,32 +7019,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>523</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7054,32 +7054,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14212</t>
+          <t>14882</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>23,12%</t>
         </is>
       </c>
     </row>
@@ -7097,32 +7097,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>835</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>8380</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7132,32 +7132,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7167,32 +7167,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>5777</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>11932</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -7210,17 +7210,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7245,17 +7245,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17552</t>
+          <t>22927</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17552</t>
+          <t>22927</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17552</t>
+          <t>22927</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7280,17 +7280,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>50494</t>
+          <t>64355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>50494</t>
+          <t>64355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>50494</t>
+          <t>64355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7327,32 +7327,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>38243</t>
+          <t>45841</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10625</t>
+          <t>33470</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82680</t>
+          <t>62537</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7362,32 +7362,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>50756</t>
+          <t>62904</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40918</t>
+          <t>51717</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62809</t>
+          <t>77449</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7397,32 +7397,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>88999</t>
+          <t>108745</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35981</t>
+          <t>91514</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140697</t>
+          <t>128747</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -7440,32 +7440,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42379</t>
+          <t>46026</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10796</t>
+          <t>32947</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90263</t>
+          <t>61616</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7475,32 +7475,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36515</t>
+          <t>39240</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26313</t>
+          <t>28651</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48019</t>
+          <t>50898</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7510,32 +7510,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>78894</t>
+          <t>85266</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28912</t>
+          <t>67484</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127970</t>
+          <t>104865</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -7553,32 +7553,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>78372</t>
+          <t>83802</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21369</t>
+          <t>67847</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>159470</t>
+          <t>103462</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7588,32 +7588,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62025</t>
+          <t>66274</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51407</t>
+          <t>55306</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>73970</t>
+          <t>79434</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7623,32 +7623,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>140397</t>
+          <t>150075</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>57692</t>
+          <t>128576</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>221498</t>
+          <t>170990</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>31,02%</t>
         </is>
       </c>
     </row>
@@ -7666,32 +7666,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45640</t>
+          <t>50262</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12623</t>
+          <t>37192</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94580</t>
+          <t>66229</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7701,32 +7701,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36760</t>
+          <t>38075</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27863</t>
+          <t>28851</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47686</t>
+          <t>49703</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7736,32 +7736,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>82400</t>
+          <t>88337</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33759</t>
+          <t>71540</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130037</t>
+          <t>107679</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -7779,32 +7779,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>307169</t>
+          <t>71473</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>111435</t>
+          <t>56103</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>454710</t>
+          <t>89991</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7814,32 +7814,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>42227</t>
+          <t>47251</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30979</t>
+          <t>36544</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53834</t>
+          <t>59853</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7849,32 +7849,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>349396</t>
+          <t>118724</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146930</t>
+          <t>100013</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>582946</t>
+          <t>139965</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -7892,17 +7892,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>511804</t>
+          <t>297403</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>511804</t>
+          <t>297403</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>511804</t>
+          <t>297403</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7927,17 +7927,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>228283</t>
+          <t>253744</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>228283</t>
+          <t>253744</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>228283</t>
+          <t>253744</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7962,17 +7962,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>740087</t>
+          <t>551147</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>740087</t>
+          <t>551147</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>740087</t>
+          <t>551147</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8009,32 +8009,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>20344</t>
+          <t>21500</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12448</t>
+          <t>13485</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30855</t>
+          <t>34181</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8044,32 +8044,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18053</t>
+          <t>19963</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11947</t>
+          <t>13087</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>27383</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8079,32 +8079,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>38397</t>
+          <t>41463</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28677</t>
+          <t>30593</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51080</t>
+          <t>54413</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -8122,32 +8122,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9745</t>
+          <t>11143</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18682</t>
+          <t>19752</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8157,32 +8157,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13628</t>
+          <t>14536</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8192,32 +8192,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>17211</t>
+          <t>19809</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>12750</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27129</t>
+          <t>30409</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -8235,32 +8235,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31078</t>
+          <t>33746</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21974</t>
+          <t>22126</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43264</t>
+          <t>46287</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8270,32 +8270,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24238</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17690</t>
+          <t>19859</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32745</t>
+          <t>35854</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8305,32 +8305,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>55316</t>
+          <t>60812</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>43683</t>
+          <t>47560</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>69462</t>
+          <t>74985</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -8348,32 +8348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24294</t>
+          <t>27627</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15713</t>
+          <t>18915</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34188</t>
+          <t>38395</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8383,32 +8383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>28314</t>
+          <t>29810</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21201</t>
+          <t>21692</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38516</t>
+          <t>39642</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8418,32 +8418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>52608</t>
+          <t>57437</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42050</t>
+          <t>46186</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66477</t>
+          <t>73653</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -8461,32 +8461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>38365</t>
+          <t>44327</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27440</t>
+          <t>33151</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51243</t>
+          <t>59276</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8496,32 +8496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>26950</t>
+          <t>28995</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19725</t>
+          <t>20985</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35853</t>
+          <t>38153</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8531,32 +8531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>65314</t>
+          <t>73322</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>59518</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>81163</t>
+          <t>90067</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,62%</t>
         </is>
       </c>
     </row>
@@ -8574,17 +8574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>123826</t>
+          <t>138343</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>123826</t>
+          <t>138343</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>123826</t>
+          <t>138343</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8609,17 +8609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>105020</t>
+          <t>114500</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>105020</t>
+          <t>114500</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>105020</t>
+          <t>114500</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8644,17 +8644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>228846</t>
+          <t>252843</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>228846</t>
+          <t>252843</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>228846</t>
+          <t>252843</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8691,32 +8691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>62842</t>
+          <t>78368</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23300</t>
+          <t>61180</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>108235</t>
+          <t>99375</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8726,32 +8726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>72784</t>
+          <t>88201</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60567</t>
+          <t>74055</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88193</t>
+          <t>103959</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8761,32 +8761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>135626</t>
+          <t>166569</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>68980</t>
+          <t>143891</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>187023</t>
+          <t>191709</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -8804,32 +8804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>56812</t>
+          <t>62290</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20959</t>
+          <t>46794</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>97375</t>
+          <t>81325</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8839,32 +8839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>45819</t>
+          <t>52701</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36178</t>
+          <t>42450</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>59361</t>
+          <t>66731</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8874,32 +8874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>102632</t>
+          <t>114991</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>50455</t>
+          <t>94631</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>142421</t>
+          <t>137619</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -8917,32 +8917,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>124128</t>
+          <t>133253</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42669</t>
+          <t>111414</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>210385</t>
+          <t>156214</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8952,32 +8952,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>93597</t>
+          <t>101164</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>80545</t>
+          <t>86884</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>109631</t>
+          <t>118365</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8987,32 +8987,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>217724</t>
+          <t>234417</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>105231</t>
+          <t>206926</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>299847</t>
+          <t>262761</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -9030,32 +9030,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>76083</t>
+          <t>84181</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28124</t>
+          <t>66857</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>131535</t>
+          <t>104079</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9065,32 +9065,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>66874</t>
+          <t>69818</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55006</t>
+          <t>57080</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>80689</t>
+          <t>84021</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9100,32 +9100,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>142957</t>
+          <t>153999</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>72786</t>
+          <t>133192</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>197186</t>
+          <t>178900</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -9143,32 +9143,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>348708</t>
+          <t>119083</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>152053</t>
+          <t>99057</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>552389</t>
+          <t>143228</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9178,32 +9178,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>71780</t>
+          <t>79286</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58402</t>
+          <t>64088</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>86973</t>
+          <t>95334</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9213,32 +9213,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>420487</t>
+          <t>198369</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>222639</t>
+          <t>171453</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>714739</t>
+          <t>227594</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -9256,17 +9256,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>668573</t>
+          <t>477175</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>668573</t>
+          <t>477175</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>668573</t>
+          <t>477175</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9291,17 +9291,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>350855</t>
+          <t>391170</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>350855</t>
+          <t>391170</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>350855</t>
+          <t>391170</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9326,17 +9326,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1019427</t>
+          <t>868346</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1019427</t>
+          <t>868346</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1019427</t>
+          <t>868346</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
